--- a/utils/monday_sprint_sprint_2023-13.xlsx
+++ b/utils/monday_sprint_sprint_2023-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="145">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>19/06/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>02/07/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>18819</t>
+    <t>4659500435</t>
   </si>
   <si>
     <t>Criação de base de dados de Roteiro de Produção a partir do agrupamento de etapas</t>
@@ -114,7 +114,10 @@
     <t>16/06/2023</t>
   </si>
   <si>
-    <t>20575</t>
+    <t>20/06/2023</t>
+  </si>
+  <si>
+    <t>4659506402</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -123,7 +126,10 @@
     <t>Qlik Sense Análise Crítica</t>
   </si>
   <si>
-    <t>16681</t>
+    <t>28/06/2023</t>
+  </si>
+  <si>
+    <t>4378236977</t>
   </si>
   <si>
     <t>Criação das causas raizes sistema SPS</t>
@@ -132,13 +138,16 @@
     <t>27/04/2023</t>
   </si>
   <si>
+    <t>29/06/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>20011</t>
+    <t>4503748624</t>
   </si>
   <si>
     <t>Bloqueio movimentação</t>
@@ -147,10 +156,13 @@
     <t>19/05/2023</t>
   </si>
   <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
     <t>Maio</t>
   </si>
   <si>
-    <t>20420</t>
+    <t>4580892338</t>
   </si>
   <si>
     <t>Apontamento de Inspeção</t>
@@ -162,13 +174,13 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>20589</t>
+    <t>4581576482</t>
   </si>
   <si>
     <t>Rastreabilidade Terceiros SPS</t>
   </si>
   <si>
-    <t>20638</t>
+    <t>4589315507</t>
   </si>
   <si>
     <t>Atalho para o sistema PID no PCP</t>
@@ -177,7 +189,7 @@
     <t>05/06/2023</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4672904921</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -186,10 +198,10 @@
     <t>Entrada: desenvolver a união dos conjuntos e visualizar o procedimento de embalagem</t>
   </si>
   <si>
-    <t>20/06/2023</t>
-  </si>
-  <si>
-    <t>8474</t>
+    <t>26/06/2023</t>
+  </si>
+  <si>
+    <t>4665403369</t>
   </si>
   <si>
     <t>Análise</t>
@@ -198,21 +210,27 @@
     <t>Tempos de Roteiro</t>
   </si>
   <si>
-    <t>20798</t>
+    <t>4657011719</t>
   </si>
   <si>
     <t>Projeto FATURA - Revisão do cálculo de agrupamento de etapas do Cenário 2 e 3</t>
   </si>
   <si>
+    <t>27/06/2023</t>
+  </si>
+  <si>
     <t>4669204416</t>
   </si>
   <si>
-    <t>18985</t>
+    <t>4659163080</t>
   </si>
   <si>
     <t>Sistema Deltractor - Integração com Andon</t>
   </si>
   <si>
+    <t>4581817403</t>
+  </si>
+  <si>
     <t>Novo Recurso</t>
   </si>
   <si>
@@ -222,6 +240,9 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>4638182338</t>
+  </si>
+  <si>
     <t>Extrações Deltractor</t>
   </si>
   <si>
@@ -237,58 +258,73 @@
     <t>Sistema Deltractor - Dashboard</t>
   </si>
   <si>
+    <t>4672913744</t>
+  </si>
+  <si>
     <t>Visualizar o estoque a partir do tablet</t>
   </si>
   <si>
+    <t>4672916712</t>
+  </si>
+  <si>
     <t>Consultar em qual box está a sequencia. onde esta a caixa</t>
   </si>
   <si>
+    <t>4672922410</t>
+  </si>
+  <si>
     <t>Migrar relatórios do ambiente desktop para web</t>
   </si>
   <si>
+    <t>4672908970</t>
+  </si>
+  <si>
     <t>Migrar rotina de geração e entrada dos conjuntos no depósito</t>
   </si>
   <si>
     <t>4669204505</t>
   </si>
   <si>
-    <t>20747</t>
+    <t>4658345378</t>
   </si>
   <si>
     <t>Requisição Eletrodo</t>
   </si>
   <si>
-    <t>20661</t>
+    <t>4665242464</t>
   </si>
   <si>
     <t>Quando a SIC estourar orçamento, ela deverá ir para o Diretor, independente do valor</t>
   </si>
   <si>
-    <t>18228</t>
+    <t>4665640065</t>
   </si>
   <si>
     <t>Sistemas de corridas</t>
   </si>
   <si>
-    <t>20799</t>
+    <t>4656996463</t>
   </si>
   <si>
     <t>Carteira de Pedido Conjunto e Componente</t>
   </si>
   <si>
-    <t>20790</t>
+    <t>21/06/2023</t>
+  </si>
+  <si>
+    <t>4657028620</t>
   </si>
   <si>
     <t>Melhoria sistema de corridas</t>
   </si>
   <si>
-    <t>20713</t>
+    <t>4657079337</t>
   </si>
   <si>
     <t>Inclusão de campo no apontamento de horas de maquina parada</t>
   </si>
   <si>
-    <t>20804</t>
+    <t>4657919135</t>
   </si>
   <si>
     <t>Melhorias lançamento consignados</t>
@@ -297,19 +333,19 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>20800</t>
+    <t>4658310835</t>
   </si>
   <si>
     <t>Alteração de Faturamento S/N - Digitação da NF</t>
   </si>
   <si>
-    <t>20295</t>
+    <t>4672799411</t>
   </si>
   <si>
     <t>Informações de triangulação empresas Grupo Altona</t>
   </si>
   <si>
-    <t>20904</t>
+    <t>4695024459</t>
   </si>
   <si>
     <t>Inclusão de campos na integração de NFs Faturamento</t>
@@ -318,13 +354,16 @@
     <t>23/06/2023</t>
   </si>
   <si>
+    <t>22/06/2023</t>
+  </si>
+  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-13</t>
+    <t>Abr/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -391,6 +430,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -966,7 +1008,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -983,22 +1025,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1013,7 +1055,7 @@
         <v>32</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1030,22 +1072,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1057,10 +1099,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1069,30 +1111,30 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1104,10 +1146,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1119,27 +1161,27 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1151,10 +1193,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1163,7 +1205,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1171,22 +1213,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1198,11 +1240,11 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1210,7 +1252,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1218,46 +1260,46 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1265,22 +1307,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1292,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1312,22 +1354,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1342,7 +1384,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1359,22 +1401,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1389,7 +1431,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1406,7 +1448,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1453,22 +1495,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1483,7 +1525,7 @@
         <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1500,25 +1542,25 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1527,10 +1569,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1539,7 +1581,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1547,25 +1589,25 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1574,10 +1616,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1586,7 +1628,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1594,22 +1636,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -1621,10 +1663,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1633,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1641,22 +1683,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1668,10 +1710,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1688,22 +1730,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -1715,10 +1757,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1735,22 +1777,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -1762,10 +1804,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1782,22 +1824,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -1809,10 +1851,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1829,7 +1871,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1876,22 +1918,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -1906,7 +1948,7 @@
         <v>32</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1923,25 +1965,25 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1953,7 +1995,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1970,22 +2012,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2000,7 +2042,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2017,22 +2059,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2047,7 +2089,7 @@
         <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2064,22 +2106,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2094,7 +2136,7 @@
         <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2111,22 +2153,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2141,7 +2183,7 @@
         <v>32</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2158,25 +2200,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2188,7 +2230,7 @@
         <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2205,22 +2247,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2235,7 +2277,7 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2252,22 +2294,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2279,10 +2321,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2299,22 +2341,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2326,10 +2368,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2338,7 +2380,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2357,23 +2399,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2381,16 +2423,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2401,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2409,7 +2451,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2422,7 +2464,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2430,7 +2472,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2461,12 +2503,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>31</v>
@@ -2480,7 +2522,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2490,25 +2532,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2519,19 +2561,19 @@
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2543,21 +2585,21 @@
         <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -2569,16 +2611,16 @@
         <v>31</v>
       </c>
       <c r="M11" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2595,53 +2637,53 @@
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="Q12">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2653,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="M14" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2661,7 +2703,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2669,7 +2711,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2677,7 +2719,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2685,10 +2727,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2696,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2710,7 +2752,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -2718,128 +2760,128 @@
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
